--- a/artfynd/A 21002-2025 artfynd.xlsx
+++ b/artfynd/A 21002-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125405805</v>
+        <v>125405253</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,7 +718,7 @@
         <v>583676</v>
       </c>
       <c r="R2" t="n">
-        <v>7077334</v>
+        <v>7077354</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125405200</v>
+        <v>125405372</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,34 +905,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rinnloken, Rinnloken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583679</v>
+        <v>583662</v>
       </c>
       <c r="R4" t="n">
-        <v>7077361</v>
+        <v>7077343</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -965,6 +970,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125405112</v>
+        <v>125405805</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583668</v>
+        <v>583676</v>
       </c>
       <c r="R5" t="n">
-        <v>7077364</v>
+        <v>7077334</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1093,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125405372</v>
+        <v>125404991</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1138,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583662</v>
+        <v>583657</v>
       </c>
       <c r="R6" t="n">
-        <v>7077343</v>
+        <v>7077400</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1178,7 +1188,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gamla ringhack, gran</t>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125405830</v>
+        <v>125405112</v>
       </c>
       <c r="B7" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1227,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583679</v>
+        <v>583668</v>
       </c>
       <c r="R7" t="n">
-        <v>7077328</v>
+        <v>7077364</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1307,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125405253</v>
+        <v>125405200</v>
       </c>
       <c r="B8" t="n">
         <v>91012</v>
@@ -1347,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583676</v>
+        <v>583679</v>
       </c>
       <c r="R8" t="n">
-        <v>7077354</v>
+        <v>7077361</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1409,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125404991</v>
+        <v>125405830</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,43 +1431,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rinnloken, Rinnloken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583657</v>
+        <v>583679</v>
       </c>
       <c r="R9" t="n">
-        <v>7077400</v>
+        <v>7077328</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1490,11 +1495,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125405601</v>
+        <v>125405190</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>79919</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1533,25 +1533,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6461</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583693</v>
+        <v>583674</v>
       </c>
       <c r="R10" t="n">
-        <v>7077339</v>
+        <v>7077355</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1623,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125405190</v>
+        <v>125405601</v>
       </c>
       <c r="B11" t="n">
-        <v>79919</v>
+        <v>91030</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1635,25 +1635,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583674</v>
+        <v>583693</v>
       </c>
       <c r="R11" t="n">
-        <v>7077355</v>
+        <v>7077339</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>

--- a/artfynd/A 21002-2025 artfynd.xlsx
+++ b/artfynd/A 21002-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125405253</v>
+        <v>125405112</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583676</v>
+        <v>583668</v>
       </c>
       <c r="R2" t="n">
-        <v>7077354</v>
+        <v>7077364</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125405476</v>
+        <v>125405601</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>91184</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rinnloken, Rinnloken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583657</v>
+        <v>583693</v>
       </c>
       <c r="R3" t="n">
-        <v>7077329</v>
+        <v>7077339</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -858,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Nyligen gjort bohål, gran. 3.5m upp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125405372</v>
+        <v>125405190</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>80056</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,43 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rinnloken, Rinnloken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583662</v>
+        <v>583674</v>
       </c>
       <c r="R4" t="n">
-        <v>7077343</v>
+        <v>7077355</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -970,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125405805</v>
+        <v>125405372</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>57635</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,34 +997,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rinnloken, Rinnloken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583676</v>
+        <v>583662</v>
       </c>
       <c r="R5" t="n">
-        <v>7077334</v>
+        <v>7077343</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1077,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125404991</v>
+        <v>125405830</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>91131</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,43 +1105,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rinnloken, Rinnloken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583657</v>
+        <v>583679</v>
       </c>
       <c r="R6" t="n">
-        <v>7077400</v>
+        <v>7077328</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1184,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125405112</v>
+        <v>125405476</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>57635</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,34 +1211,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rinnloken, Rinnloken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583668</v>
+        <v>583657</v>
       </c>
       <c r="R7" t="n">
-        <v>7077364</v>
+        <v>7077329</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1291,6 +1276,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Nyligen gjort bohål, gran. 3.5m upp</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125405200</v>
+        <v>125405253</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583679</v>
+        <v>583676</v>
       </c>
       <c r="R8" t="n">
-        <v>7077361</v>
+        <v>7077354</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1419,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125405830</v>
+        <v>125405200</v>
       </c>
       <c r="B9" t="n">
-        <v>90977</v>
+        <v>91166</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1431,25 +1421,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,7 +1452,7 @@
         <v>583679</v>
       </c>
       <c r="R9" t="n">
-        <v>7077328</v>
+        <v>7077361</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1521,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125405190</v>
+        <v>125404991</v>
       </c>
       <c r="B10" t="n">
-        <v>79919</v>
+        <v>57635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1533,38 +1523,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rinnloken, Rinnloken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583674</v>
+        <v>583657</v>
       </c>
       <c r="R10" t="n">
-        <v>7077355</v>
+        <v>7077400</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1597,6 +1592,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125405601</v>
+        <v>125405805</v>
       </c>
       <c r="B11" t="n">
-        <v>91030</v>
+        <v>91184</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583693</v>
+        <v>583676</v>
       </c>
       <c r="R11" t="n">
-        <v>7077339</v>
+        <v>7077334</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>

--- a/artfynd/A 21002-2025 artfynd.xlsx
+++ b/artfynd/A 21002-2025 artfynd.xlsx
@@ -1511,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125404991</v>
+        <v>125405805</v>
       </c>
       <c r="B10" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,39 +1527,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rinnloken, Rinnloken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583657</v>
+        <v>583676</v>
       </c>
       <c r="R10" t="n">
-        <v>7077400</v>
+        <v>7077334</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1592,11 +1587,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125405805</v>
+        <v>125404991</v>
       </c>
       <c r="B11" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,34 +1629,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rinnloken, Rinnloken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583676</v>
+        <v>583657</v>
       </c>
       <c r="R11" t="n">
-        <v>7077334</v>
+        <v>7077400</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1699,6 +1694,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 21002-2025 artfynd.xlsx
+++ b/artfynd/A 21002-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125405112</v>
+        <v>125405476</v>
       </c>
       <c r="B2" t="n">
-        <v>91166</v>
+        <v>57635</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rinnloken, Rinnloken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583668</v>
+        <v>583657</v>
       </c>
       <c r="R2" t="n">
-        <v>7077364</v>
+        <v>7077329</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -751,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Nyligen gjort bohål, gran. 3.5m upp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125405601</v>
+        <v>125404991</v>
       </c>
       <c r="B3" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rinnloken, Rinnloken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583693</v>
+        <v>583657</v>
       </c>
       <c r="R3" t="n">
-        <v>7077339</v>
+        <v>7077400</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -853,6 +868,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125405190</v>
+        <v>125405601</v>
       </c>
       <c r="B4" t="n">
-        <v>80056</v>
+        <v>91184</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6461</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583674</v>
+        <v>583693</v>
       </c>
       <c r="R4" t="n">
-        <v>7077355</v>
+        <v>7077339</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125405372</v>
+        <v>125405253</v>
       </c>
       <c r="B5" t="n">
-        <v>57635</v>
+        <v>91166</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,39 +1017,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rinnloken, Rinnloken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583662</v>
+        <v>583676</v>
       </c>
       <c r="R5" t="n">
-        <v>7077343</v>
+        <v>7077354</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1062,11 +1077,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125405830</v>
+        <v>125405805</v>
       </c>
       <c r="B6" t="n">
-        <v>91131</v>
+        <v>91184</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1115,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583679</v>
+        <v>583676</v>
       </c>
       <c r="R6" t="n">
-        <v>7077328</v>
+        <v>7077334</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1195,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125405476</v>
+        <v>125405830</v>
       </c>
       <c r="B7" t="n">
-        <v>57635</v>
+        <v>91131</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,43 +1217,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rinnloken, Rinnloken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583657</v>
+        <v>583679</v>
       </c>
       <c r="R7" t="n">
-        <v>7077329</v>
+        <v>7077328</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1276,11 +1281,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Nyligen gjort bohål, gran. 3.5m upp</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125405253</v>
+        <v>125405200</v>
       </c>
       <c r="B8" t="n">
         <v>91166</v>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583676</v>
+        <v>583679</v>
       </c>
       <c r="R8" t="n">
-        <v>7077354</v>
+        <v>7077361</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125405200</v>
+        <v>125405372</v>
       </c>
       <c r="B9" t="n">
-        <v>91166</v>
+        <v>57635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,34 +1425,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rinnloken, Rinnloken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583679</v>
+        <v>583662</v>
       </c>
       <c r="R9" t="n">
-        <v>7077361</v>
+        <v>7077343</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1485,6 +1490,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125405805</v>
+        <v>125405112</v>
       </c>
       <c r="B10" t="n">
-        <v>91184</v>
+        <v>91166</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583676</v>
+        <v>583668</v>
       </c>
       <c r="R10" t="n">
-        <v>7077334</v>
+        <v>7077364</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1613,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125404991</v>
+        <v>125405190</v>
       </c>
       <c r="B11" t="n">
-        <v>57635</v>
+        <v>80056</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1625,43 +1635,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rinnloken, Rinnloken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583657</v>
+        <v>583674</v>
       </c>
       <c r="R11" t="n">
-        <v>7077400</v>
+        <v>7077355</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1694,11 +1699,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 21002-2025 artfynd.xlsx
+++ b/artfynd/A 21002-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125405476</v>
+        <v>125405601</v>
       </c>
       <c r="B2" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rinnloken, Rinnloken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583657</v>
+        <v>583693</v>
       </c>
       <c r="R2" t="n">
-        <v>7077329</v>
+        <v>7077339</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -756,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Nyligen gjort bohål, gran. 3.5m upp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125404991</v>
+        <v>125405372</v>
       </c>
       <c r="B3" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583657</v>
+        <v>583662</v>
       </c>
       <c r="R3" t="n">
-        <v>7077400</v>
+        <v>7077343</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -872,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack, gran</t>
+          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125405601</v>
+        <v>125405805</v>
       </c>
       <c r="B4" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91238</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583693</v>
+        <v>583676</v>
       </c>
       <c r="R4" t="n">
-        <v>7077339</v>
+        <v>7077334</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1004,12 +979,7 @@
         <v>125405253</v>
       </c>
       <c r="B5" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,37 +1073,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125405805</v>
+        <v>125405190</v>
       </c>
       <c r="B6" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80098</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6461</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583676</v>
+        <v>583674</v>
       </c>
       <c r="R6" t="n">
-        <v>7077334</v>
+        <v>7077355</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1205,37 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125405830</v>
+        <v>125405112</v>
       </c>
       <c r="B7" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583679</v>
+        <v>583668</v>
       </c>
       <c r="R7" t="n">
-        <v>7077328</v>
+        <v>7077364</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1307,15 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125405200</v>
+        <v>125405476</v>
       </c>
       <c r="B8" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,34 +1278,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rinnloken, Rinnloken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583679</v>
+        <v>583657</v>
       </c>
       <c r="R8" t="n">
-        <v>7077361</v>
+        <v>7077329</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1383,6 +1343,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Nyligen gjort bohål, gran. 3.5m upp</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,15 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125405372</v>
+        <v>125404991</v>
       </c>
       <c r="B9" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583662</v>
+        <v>583657</v>
       </c>
       <c r="R9" t="n">
-        <v>7077343</v>
+        <v>7077400</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1494,7 +1454,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Gamla ringhack, gran</t>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,37 +1481,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125405112</v>
+        <v>125405830</v>
       </c>
       <c r="B10" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91185</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583668</v>
+        <v>583679</v>
       </c>
       <c r="R10" t="n">
-        <v>7077364</v>
+        <v>7077328</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1623,37 +1578,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125405190</v>
+        <v>125405200</v>
       </c>
       <c r="B11" t="n">
-        <v>80056</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583674</v>
+        <v>583679</v>
       </c>
       <c r="R11" t="n">
-        <v>7077355</v>
+        <v>7077361</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>

--- a/artfynd/A 21002-2025 artfynd.xlsx
+++ b/artfynd/A 21002-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125405601</v>
       </c>
       <c r="B2" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125405805</v>
       </c>
       <c r="B4" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>125405253</v>
       </c>
       <c r="B5" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>125405112</v>
       </c>
       <c r="B7" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>125405830</v>
       </c>
       <c r="B10" t="n">
-        <v>91185</v>
+        <v>91192</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>125405200</v>
       </c>
       <c r="B11" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 21002-2025 artfynd.xlsx
+++ b/artfynd/A 21002-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125405601</v>
       </c>
       <c r="B2" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125405805</v>
       </c>
       <c r="B4" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>125405253</v>
       </c>
       <c r="B5" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>125405190</v>
       </c>
       <c r="B6" t="n">
-        <v>80098</v>
+        <v>80099</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>125405112</v>
       </c>
       <c r="B7" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>125405830</v>
       </c>
       <c r="B10" t="n">
-        <v>91192</v>
+        <v>91193</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>125405200</v>
       </c>
       <c r="B11" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 21002-2025 artfynd.xlsx
+++ b/artfynd/A 21002-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125405601</v>
       </c>
       <c r="B2" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125405805</v>
       </c>
       <c r="B4" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>125405253</v>
       </c>
       <c r="B5" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>125405190</v>
       </c>
       <c r="B6" t="n">
-        <v>80099</v>
+        <v>80103</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>125405112</v>
       </c>
       <c r="B7" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>125405830</v>
       </c>
       <c r="B10" t="n">
-        <v>91193</v>
+        <v>91197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>125405200</v>
       </c>
       <c r="B11" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
